--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46225.00178723379</v>
+        <v>46279.12959502314</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>239</v>
@@ -6152,8 +6152,8 @@
       <c r="R81" s="9">
         <v>46286</v>
       </c>
-      <c r="S81" s="7" t="s">
-        <v>32</v>
+      <c r="S81" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46225.00178356482</v>
+        <v>46280.15184262731</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>250</v>
@@ -6521,8 +6521,8 @@
       <c r="R88" s="5">
         <v>46287</v>
       </c>
-      <c r="S88" s="7" t="s">
-        <v>32</v>
+      <c r="S88" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -5727,7 +5727,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46274.15436547453</v>
+        <v>46281.25044606482</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>227</v>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46225.00190993056</v>
+        <v>46281.25044778935</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>148</v>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46225.00190693287</v>
+        <v>46281.250451388885</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>148</v>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46225.00190398148</v>
+        <v>46281.25045261574</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>148</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46225.00190130787</v>
+        <v>46281.25044259259</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>148</v>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46225.00189846064</v>
+        <v>46281.25044391204</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>148</v>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46225.0018940625</v>
+        <v>46281.25044478009</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>148</v>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46225.00177993056</v>
+        <v>46281.15939369213</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>262</v>
@@ -6902,8 +6902,8 @@
       <c r="R95" s="9">
         <v>46288</v>
       </c>
-      <c r="S95" s="7" t="s">
-        <v>32</v>
+      <c r="S95" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -406,6 +406,9 @@
     <t xml:space="preserve">Generacion Oc  OT 4376 ,Armado OT 4376 ,Control de calidad  OT 4376 </t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1216771893506639</t>
   </si>
   <si>
@@ -740,9 +743,6 @@
   </si>
   <si>
     <t xml:space="preserve">Revestimiento OT 4376 </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1216771795377433</t>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46224.9875411574</v>
+        <v>46282.153770081015</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>112</v>
@@ -3358,8 +3358,8 @@
       <c r="R31" s="9">
         <v>46247</v>
       </c>
-      <c r="S31" s="7" t="s">
-        <v>32</v>
+      <c r="S31" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5">
         <v>46224.89592390046</v>
@@ -3380,7 +3380,7 @@
         <v>46255.6286522338</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3410,10 +3410,10 @@
         <v>112</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33" s="9">
         <v>46224.89592935186</v>
@@ -3433,7 +3433,7 @@
         <v>46224.987624201385</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3463,10 +3463,10 @@
         <v>112</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3476,7 +3476,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46224.89593387731</v>
@@ -3486,16 +3486,16 @@
         <v>46224.98774165509</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3516,7 +3516,7 @@
         <v>112</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>112</v>
@@ -3529,7 +3529,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" s="9">
         <v>46224.89593827546</v>
@@ -3539,7 +3539,7 @@
         <v>46238.486380925926</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -3563,7 +3563,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3576,7 +3576,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46224.895942546296</v>
@@ -3588,16 +3588,16 @@
         <v>46235.17742733796</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3615,13 +3615,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3641,7 +3641,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B37" s="9">
         <v>46224.895948425925</v>
@@ -3653,16 +3653,16 @@
         <v>46242.177803032406</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -3680,13 +3680,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46224.895953506944</v>
@@ -3724,10 +3724,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I38" s="5">
         <v>46244</v>
@@ -3745,13 +3745,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="5">
         <v>46244</v>
@@ -3771,7 +3771,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" s="9">
         <v>46224.89596851852</v>
@@ -3781,16 +3781,16 @@
         <v>46224.9887275463</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I39" s="9">
         <v>46290</v>
@@ -3808,13 +3808,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q39" s="9">
         <v>46290</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46224.89597322917</v>
@@ -3844,16 +3844,16 @@
         <v>46224.98802077546</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3869,13 +3869,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3885,7 +3885,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="9">
         <v>46224.89597747685</v>
@@ -3895,16 +3895,16 @@
         <v>46224.988017592594</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9">
@@ -3920,13 +3920,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3936,7 +3936,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46224.89600425926</v>
@@ -3946,16 +3946,16 @@
         <v>46224.98801423611</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -3971,13 +3971,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3987,7 +3987,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B43" s="9">
         <v>46224.90846989583</v>
@@ -3997,16 +3997,16 @@
         <v>46224.988011203706</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="9">
@@ -4022,13 +4022,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4038,7 +4038,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B44" s="5">
         <v>46224.908482824074</v>
@@ -4048,16 +4048,16 @@
         <v>46224.98800859954</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -4073,13 +4073,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4089,7 +4089,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B45" s="9">
         <v>46224.908498171295</v>
@@ -4099,16 +4099,16 @@
         <v>46224.98800302083</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="9">
@@ -4124,13 +4124,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B46" s="5">
         <v>46224.89600854166</v>
@@ -4150,7 +4150,7 @@
         <v>46261.50044483796</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4174,7 +4174,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B47" s="9">
         <v>46224.896012384255</v>
@@ -4197,16 +4197,16 @@
         <v>46261.18572775463</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="9">
@@ -4222,13 +4222,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>93</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q47" s="9">
         <v>46260</v>
@@ -4248,7 +4248,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B48" s="5">
         <v>46224.896018368054</v>
@@ -4258,16 +4258,16 @@
         <v>46261.18572780093</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I48" s="5">
         <v>46260</v>
@@ -4285,13 +4285,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>101</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q48" s="5">
         <v>46260</v>
@@ -4311,7 +4311,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B49" s="9">
         <v>46224.89602424769</v>
@@ -4321,16 +4321,16 @@
         <v>46261.1857278588</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I49" s="9">
         <v>46260</v>
@@ -4348,13 +4348,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>109</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q49" s="9">
         <v>46260</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B50" s="5">
         <v>46224.89603097222</v>
@@ -4384,16 +4384,16 @@
         <v>46262.19370900463</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I50" s="5">
         <v>46261</v>
@@ -4411,13 +4411,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q50" s="5">
         <v>46261</v>
@@ -4437,7 +4437,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B51" s="9">
         <v>46224.89603738426</v>
@@ -4449,16 +4449,16 @@
         <v>46262.19370895834</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I51" s="9">
         <v>46261</v>
@@ -4476,13 +4476,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q51" s="9">
         <v>46261</v>
@@ -4502,7 +4502,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B52" s="5">
         <v>46224.89604363426</v>
@@ -4512,16 +4512,16 @@
         <v>46262.193708923616</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I52" s="5">
         <v>46261</v>
@@ -4539,13 +4539,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q52" s="5">
         <v>46261</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B53" s="9">
         <v>46224.89604989583</v>
@@ -4575,7 +4575,7 @@
         <v>46224.978400416665</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4599,7 +4599,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4612,7 +4612,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B54" s="5">
         <v>46224.8960534375</v>
@@ -4628,10 +4628,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46262</v>
@@ -4649,13 +4649,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q54" s="5">
         <v>46266</v>
@@ -4675,7 +4675,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B55" s="9">
         <v>46224.89605969907</v>
@@ -4685,16 +4685,16 @@
         <v>46274.16186678241</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I55" s="9">
         <v>46267</v>
@@ -4712,13 +4712,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q55" s="9">
         <v>46273</v>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B56" s="5">
         <v>46224.89606466435</v>
@@ -4748,16 +4748,16 @@
         <v>46273.16868585648</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I56" s="5">
         <v>46267</v>
@@ -4775,13 +4775,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B57" s="9">
         <v>46224.89607361111</v>
@@ -4801,16 +4801,16 @@
         <v>46273.16868825231</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I57" s="9">
         <v>46267</v>
@@ -4828,13 +4828,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4844,7 +4844,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B58" s="5">
         <v>46224.89613331019</v>
@@ -4854,16 +4854,16 @@
         <v>46273.168687094905</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I58" s="5">
         <v>46267</v>
@@ -4881,13 +4881,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4897,7 +4897,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B59" s="9">
         <v>46224.90866162037</v>
@@ -4907,16 +4907,16 @@
         <v>46273.168658738425</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I59" s="9">
         <v>46267</v>
@@ -4934,13 +4934,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>77</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4950,7 +4950,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B60" s="5">
         <v>46224.90867304398</v>
@@ -4960,16 +4960,16 @@
         <v>46273.16866001158</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I60" s="5">
         <v>46267</v>
@@ -4987,13 +4987,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5003,7 +5003,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B61" s="9">
         <v>46224.90868626157</v>
@@ -5013,16 +5013,16 @@
         <v>46273.16866116898</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I61" s="9">
         <v>46267</v>
@@ -5040,13 +5040,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>77</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5056,7 +5056,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B62" s="5">
         <v>46224.89614391203</v>
@@ -5066,16 +5066,16 @@
         <v>46275.15322010417</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5093,13 +5093,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q62" s="5">
         <v>46274</v>
@@ -5119,7 +5119,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B63" s="9">
         <v>46224.896148935186</v>
@@ -5129,16 +5129,16 @@
         <v>46274.16860311343</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I63" s="9">
         <v>46274</v>
@@ -5156,13 +5156,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5172,7 +5172,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B64" s="5">
         <v>46224.89615454861</v>
@@ -5182,16 +5182,16 @@
         <v>46274.16860428241</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I64" s="5">
         <v>46274</v>
@@ -5209,13 +5209,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5225,7 +5225,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B65" s="9">
         <v>46224.89616001157</v>
@@ -5235,16 +5235,16 @@
         <v>46274.16860553241</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I65" s="9">
         <v>46274</v>
@@ -5262,13 +5262,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B66" s="5">
         <v>46224.90877734954</v>
@@ -5288,16 +5288,16 @@
         <v>46274.168593078706</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I66" s="5">
         <v>46274</v>
@@ -5315,13 +5315,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B67" s="9">
         <v>46224.90879113426</v>
@@ -5341,16 +5341,16 @@
         <v>46274.16859423611</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I67" s="9">
         <v>46274</v>
@@ -5368,13 +5368,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B68" s="5">
         <v>46224.90880622686</v>
@@ -5394,16 +5394,16 @@
         <v>46274.16859528935</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5421,13 +5421,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5437,7 +5437,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B69" s="9">
         <v>46224.89616483796</v>
@@ -5447,7 +5447,7 @@
         <v>46224.97892864583</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>25</v>
@@ -5471,7 +5471,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>26</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B70" s="5">
         <v>46224.89616836805</v>
@@ -5494,16 +5494,16 @@
         <v>46232.190274444445</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I70" s="5">
         <v>46230</v>
@@ -5521,13 +5521,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>54</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q70" s="5">
         <v>46231</v>
@@ -5547,7 +5547,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B71" s="9">
         <v>46224.89617388889</v>
@@ -5557,16 +5557,16 @@
         <v>46232.19027465278</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I71" s="9">
         <v>46230</v>
@@ -5584,13 +5584,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q71" s="9">
         <v>46231</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B72" s="5">
         <v>46224.89617931713</v>
@@ -5620,16 +5620,16 @@
         <v>46232.19027490741</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I72" s="5">
         <v>46230</v>
@@ -5647,13 +5647,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -5673,7 +5673,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B73" s="9">
         <v>46224.896184826386</v>
@@ -5683,7 +5683,7 @@
         <v>46224.981535706014</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>25</v>
@@ -5707,7 +5707,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5720,17 +5720,17 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B74" s="5">
         <v>46224.89618846065</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46281.25044606482</v>
+        <v>46282.133995543976</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5757,13 +5757,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q74" s="5">
         <v>46281</v>
@@ -5771,8 +5771,8 @@
       <c r="R74" s="5">
         <v>46275</v>
       </c>
-      <c r="S74" s="12" t="s">
-        <v>228</v>
+      <c r="S74" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
@@ -5793,7 +5793,7 @@
         <v>46281.25044778935</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5820,10 +5820,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>230</v>
@@ -5846,7 +5846,7 @@
         <v>46281.250451388885</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5873,10 +5873,10 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>230</v>
@@ -5899,7 +5899,7 @@
         <v>46281.25045261574</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5926,10 +5926,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>233</v>
@@ -5952,7 +5952,7 @@
         <v>46281.25044259259</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5979,10 +5979,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>235</v>
@@ -6005,7 +6005,7 @@
         <v>46281.25044391204</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6032,10 +6032,10 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>235</v>
@@ -6058,7 +6058,7 @@
         <v>46281.25044478009</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6085,10 +6085,10 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>235</v>
@@ -6138,13 +6138,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q81" s="9">
         <v>46286</v>
@@ -6153,7 +6153,7 @@
         <v>46286</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
@@ -6174,7 +6174,7 @@
         <v>46238.48638170139</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6225,7 +6225,7 @@
         <v>46238.486382233794</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6276,7 +6276,7 @@
         <v>46238.486382800926</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6327,7 +6327,7 @@
         <v>46225.00341435186</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6355,7 +6355,7 @@
         <v>239</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>245</v>
@@ -6378,7 +6378,7 @@
         <v>46225.003411944446</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6406,7 +6406,7 @@
         <v>239</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>245</v>
@@ -6429,7 +6429,7 @@
         <v>46225.003407199074</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6457,7 +6457,7 @@
         <v>239</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>245</v>
@@ -6507,13 +6507,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q88" s="5">
         <v>46287</v>
@@ -6522,7 +6522,7 @@
         <v>46287</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6543,7 +6543,7 @@
         <v>46225.00360141204</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6596,7 +6596,7 @@
         <v>46225.003598587966</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6649,7 +6649,7 @@
         <v>46225.00359555555</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6702,7 +6702,7 @@
         <v>46225.003592696754</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6732,7 +6732,7 @@
         <v>250</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>253</v>
@@ -6755,7 +6755,7 @@
         <v>46225.00358984954</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6785,7 +6785,7 @@
         <v>250</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>253</v>
@@ -6808,7 +6808,7 @@
         <v>46225.003585150465</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6838,7 +6838,7 @@
         <v>250</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>260</v>
@@ -6888,13 +6888,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q95" s="9">
         <v>46288</v>
@@ -6903,7 +6903,7 @@
         <v>46288</v>
       </c>
       <c r="S95" s="12" t="s">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>46238.48637237269</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6977,7 +6977,7 @@
         <v>46238.486383379626</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7030,7 +7030,7 @@
         <v>46225.003931203704</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7083,7 +7083,7 @@
         <v>46225.003927453705</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7113,7 +7113,7 @@
         <v>262</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>269</v>
@@ -7136,7 +7136,7 @@
         <v>46225.0039243287</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7166,7 +7166,7 @@
         <v>262</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>269</v>
@@ -7189,7 +7189,7 @@
         <v>46225.003918993054</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7219,7 +7219,7 @@
         <v>262</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>269</v>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46225.00177642361</v>
+        <v>46282.153769537035</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>274</v>
@@ -7269,13 +7269,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q102" s="5">
         <v>46289</v>
@@ -7283,8 +7283,8 @@
       <c r="R102" s="5">
         <v>46289</v>
       </c>
-      <c r="S102" s="7" t="s">
-        <v>32</v>
+      <c r="S102" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="T102" s="6">
         <v>0</v>
@@ -7305,7 +7305,7 @@
         <v>46225.004084687505</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7358,7 +7358,7 @@
         <v>46225.00408194444</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7411,7 +7411,7 @@
         <v>46225.00407914352</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7464,7 +7464,7 @@
         <v>46225.00407667824</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7494,7 +7494,7 @@
         <v>274</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>281</v>
@@ -7517,7 +7517,7 @@
         <v>46225.00407431713</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7547,7 +7547,7 @@
         <v>274</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>281</v>
@@ -7570,7 +7570,7 @@
         <v>46225.00406917824</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7600,7 +7600,7 @@
         <v>274</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>281</v>
@@ -7650,13 +7650,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q109" s="9">
         <v>46293</v>
@@ -7686,7 +7686,7 @@
         <v>46225.00432578704</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7716,7 +7716,7 @@
         <v>285</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>287</v>
@@ -7739,7 +7739,7 @@
         <v>46225.00432245371</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7769,7 +7769,7 @@
         <v>285</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>287</v>
@@ -7792,7 +7792,7 @@
         <v>46225.00431880787</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7822,7 +7822,7 @@
         <v>285</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>287</v>
@@ -7845,7 +7845,7 @@
         <v>46225.00431532407</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -7875,7 +7875,7 @@
         <v>285</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>287</v>
@@ -7898,7 +7898,7 @@
         <v>46225.00431230324</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -7928,7 +7928,7 @@
         <v>285</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>287</v>
@@ -7951,7 +7951,7 @@
         <v>46225.00430677083</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -7981,7 +7981,7 @@
         <v>285</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>287</v>
@@ -8081,7 +8081,7 @@
         <v>294</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>300</v>
@@ -8114,7 +8114,7 @@
         <v>46225.00456991898</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8144,7 +8144,7 @@
         <v>297</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>302</v>
@@ -8167,7 +8167,7 @@
         <v>46225.004566655094</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8197,7 +8197,7 @@
         <v>297</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>302</v>
@@ -8220,7 +8220,7 @@
         <v>46225.00456336806</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8250,7 +8250,7 @@
         <v>297</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>302</v>
@@ -8273,7 +8273,7 @@
         <v>46225.00456075231</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8303,7 +8303,7 @@
         <v>297</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>302</v>
@@ -8326,7 +8326,7 @@
         <v>46225.00455841435</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8356,7 +8356,7 @@
         <v>297</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>302</v>
@@ -8379,7 +8379,7 @@
         <v>46225.00455403935</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8409,7 +8409,7 @@
         <v>297</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>302</v>
@@ -8495,7 +8495,7 @@
         <v>46225.00484849537</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8525,7 +8525,7 @@
         <v>309</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>312</v>
@@ -8548,7 +8548,7 @@
         <v>46225.00484502315</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8578,7 +8578,7 @@
         <v>309</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>312</v>
@@ -8601,7 +8601,7 @@
         <v>46225.0048419213</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -8631,7 +8631,7 @@
         <v>309</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>312</v>
@@ -8654,7 +8654,7 @@
         <v>46225.00483878472</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8684,7 +8684,7 @@
         <v>309</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>312</v>
@@ -8707,7 +8707,7 @@
         <v>46225.00483302084</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -8737,7 +8737,7 @@
         <v>309</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>312</v>
@@ -8760,7 +8760,7 @@
         <v>46225.004831886574</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -8790,7 +8790,7 @@
         <v>309</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>312</v>
@@ -8819,10 +8819,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I131" s="9">
         <v>46296</v>
@@ -8843,7 +8843,7 @@
         <v>294</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>294</v>
@@ -8876,16 +8876,16 @@
         <v>46225.00519546296</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I132" s="5">
         <v>46296</v>
@@ -8906,7 +8906,7 @@
         <v>319</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>321</v>
@@ -8929,16 +8929,16 @@
         <v>46225.00519261574</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I133" s="9">
         <v>46296</v>
@@ -8959,7 +8959,7 @@
         <v>319</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P133" s="10" t="s">
         <v>321</v>
@@ -8982,16 +8982,16 @@
         <v>46225.00518949074</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I134" s="5">
         <v>46296</v>
@@ -9012,7 +9012,7 @@
         <v>319</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>321</v>
@@ -9035,16 +9035,16 @@
         <v>46225.00518663194</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I135" s="9">
         <v>46296</v>
@@ -9065,7 +9065,7 @@
         <v>319</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>321</v>
@@ -9088,16 +9088,16 @@
         <v>46225.0051837963</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I136" s="5">
         <v>46296</v>
@@ -9118,7 +9118,7 @@
         <v>319</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>321</v>
@@ -9141,16 +9141,16 @@
         <v>46225.00517873843</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I137" s="9">
         <v>46296</v>
@@ -9171,7 +9171,7 @@
         <v>319</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P137" s="10" t="s">
         <v>321</v>
@@ -9200,10 +9200,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I138" s="5">
         <v>46297</v>
@@ -9224,7 +9224,7 @@
         <v>294</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>329</v>
@@ -9257,16 +9257,16 @@
         <v>46225.00578898148</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I139" s="9">
         <v>46297</v>
@@ -9287,7 +9287,7 @@
         <v>328</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>331</v>
@@ -9310,16 +9310,16 @@
         <v>46225.00578587963</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I140" s="5">
         <v>46297</v>
@@ -9340,7 +9340,7 @@
         <v>328</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>331</v>
@@ -9363,16 +9363,16 @@
         <v>46225.005782395834</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I141" s="9">
         <v>46297</v>
@@ -9393,7 +9393,7 @@
         <v>328</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>331</v>
@@ -9416,16 +9416,16 @@
         <v>46225.00577939815</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I142" s="5">
         <v>46297</v>
@@ -9446,7 +9446,7 @@
         <v>328</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>328</v>
@@ -9469,16 +9469,16 @@
         <v>46225.00577614583</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I143" s="9">
         <v>46297</v>
@@ -9499,7 +9499,7 @@
         <v>328</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P143" s="10" t="s">
         <v>328</v>
@@ -9522,16 +9522,16 @@
         <v>46225.005771516204</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I144" s="5">
         <v>46297</v>
@@ -9552,7 +9552,7 @@
         <v>328</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>328</v>
